--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487476_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487476_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5813</v>
+        <v>1.6526</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1906</v>
+        <v>3.3688</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6093</v>
+        <v>-1.7162</v>
       </c>
       <c r="G2" t="n">
         <v>2.398</v>
@@ -610,13 +610,13 @@
         <v>1.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0288</v>
+        <v>0.207</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1001</v>
+        <v>-0.207</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9412</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4216</v>
+        <v>0.309</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2348</v>
+        <v>-0.3206</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6564</v>
+        <v>0.6296</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0086</v>
@@ -688,13 +688,13 @@
         <v>0.9792</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0592</v>
+        <v>-0.0534</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3258</v>
+        <v>0.24</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2666</v>
+        <v>-0.2933</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6083</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CACHOPAS GIL PRATES</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7131</v>
+        <v>-1.3269</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3279</v>
+        <v>0.8094</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.041</v>
+        <v>-2.1363</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3928</v>
+        <v>-0.9232</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5427</v>
+        <v>-1.1045</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.9355</v>
+        <v>0.1813</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3478</v>
+        <v>1.9621</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3333</v>
+        <v>-0.3608</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0145</v>
+        <v>2.3229</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7406</v>
+        <v>-2.8853</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2094</v>
+        <v>-0.7437</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.9499</v>
+        <v>-2.1416</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3709</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5011</v>
+        <v>-0.2079</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8763</v>
+        <v>-0.1735</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6248</v>
+        <v>-0.0344</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5495</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.0415</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3329</v>
+        <v>-1.3402</v>
       </c>
       <c r="E6" t="n">
-        <v>0.75</v>
+        <v>-0.1029</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0829</v>
+        <v>-1.2372</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9232</v>
+        <v>0.9435</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1045</v>
+        <v>3.0106</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1813</v>
+        <v>-2.0671</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9621</v>
+        <v>2.005</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3608</v>
+        <v>2.87</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3229</v>
+        <v>-0.865</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8853</v>
+        <v>-1.0615</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7437</v>
+        <v>0.1406</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1416</v>
+        <v>-1.2021</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2138</v>
+        <v>-0.7537</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2329</v>
+        <v>-0.1494</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0191</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>M. CACHOPAS GIL PRATES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8148</v>
+        <v>-1.5942</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6311</v>
+        <v>0.6874</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1838</v>
+        <v>-2.2815</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9435</v>
+        <v>-2.3928</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0106</v>
+        <v>0.5427</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0671</v>
+        <v>-2.9355</v>
       </c>
       <c r="J7" t="n">
-        <v>2.005</v>
+        <v>0.3478</v>
       </c>
       <c r="K7" t="n">
-        <v>2.87</v>
+        <v>0.3333</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.865</v>
+        <v>0.0145</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0615</v>
+        <v>-2.7406</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1406</v>
+        <v>0.2094</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2021</v>
+        <v>-2.9499</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9792</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9792</v>
+        <v>1.5668</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2284</v>
+        <v>0.62</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6775</v>
+        <v>0.2358</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5508</v>
+        <v>0.3842</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5507</v>
+        <v>1.5495</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.0415</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5507</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2735</v>
+        <v>-2.4572</v>
       </c>
       <c r="E8" t="n">
-        <v>0.644</v>
+        <v>0.3535</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9176</v>
+        <v>-2.8106</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4136</v>
@@ -1078,13 +1078,13 @@
         <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3092</v>
+        <v>-0.4929</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5681</v>
+        <v>0.2776</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8774</v>
+        <v>-0.7705</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5507</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7611</v>
+        <v>-2.4878</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0541</v>
+        <v>0.0053</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.707</v>
+        <v>-2.4931</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4869</v>
@@ -1156,13 +1156,13 @@
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.962</v>
+        <v>-0.6887</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4288</v>
+        <v>-0.3694</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5332</v>
+        <v>-0.3194</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3329</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8354</v>
+        <v>-3.2004</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8797</v>
+        <v>-3.3516</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0443</v>
+        <v>0.1512</v>
       </c>
       <c r="G10" t="n">
         <v>-3.8055</v>
@@ -1234,13 +1234,13 @@
         <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0091</v>
+        <v>-0.3741</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5346</v>
+        <v>-0.0065</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4745</v>
+        <v>-0.3676</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>J. FERNANDEZ PILLADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2152</v>
+        <v>-3.5658</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2677</v>
+        <v>-2.2436</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9475</v>
+        <v>-1.3222</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6784</v>
+        <v>-3.9506</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4563</v>
+        <v>-1.6622</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2221</v>
+        <v>-2.2885</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8566</v>
+        <v>-1.7454</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0991</v>
+        <v>-1.8715</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2425</v>
+        <v>0.1261</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8218</v>
+        <v>-2.2052</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3572</v>
+        <v>0.2094</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4646</v>
+        <v>-2.4145</v>
       </c>
       <c r="P11" t="n">
         <v>1.1751</v>
@@ -1312,28 +1312,28 @@
         <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.22</v>
+        <v>-0.5149</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4111</v>
+        <v>-0.4982</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1911</v>
+        <v>-0.0168</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.492</v>
+        <v>-0.2754</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.492</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ PILLADO</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2497</v>
+        <v>-3.9941</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8741</v>
+        <v>-1.0466</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3757</v>
+        <v>-2.9475</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9506</v>
+        <v>-3.6784</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6622</v>
+        <v>-2.4563</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2885</v>
+        <v>-1.2221</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7454</v>
+        <v>-0.8566</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.8715</v>
+        <v>-1.0991</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1261</v>
+        <v>0.2425</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2052</v>
+        <v>-2.8218</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2094</v>
+        <v>-1.3572</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.4145</v>
+        <v>-1.4646</v>
       </c>
       <c r="P12" t="n">
         <v>1.1751</v>
@@ -1390,22 +1390,22 @@
         <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1989</v>
+        <v>0.0012</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1286</v>
+        <v>-0.19</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0702</v>
+        <v>0.1911</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.0564</v>
+        <v>-17.8686</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.029</v>
+        <v>-1.8409</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.0277</v>
+        <v>-16.0274</v>
       </c>
       <c r="G13" t="n">
         <v>-13.1817</v>
@@ -1453,7 +1453,7 @@
         <v>-17.3592</v>
       </c>
       <c r="N13" t="n">
-        <v>0.04159999999999983</v>
+        <v>0.04159999999999986</v>
       </c>
       <c r="O13" t="n">
         <v>-17.4007</v>
@@ -1462,19 +1462,19 @@
         <v>0.9793000000000003</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.792300000000001</v>
+        <v>-9.792299999999999</v>
       </c>
       <c r="R13" t="n">
         <v>10.7715</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.652400000000001</v>
+        <v>-2.4644</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6145</v>
+        <v>-0.4266</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0378</v>
+        <v>-2.038</v>
       </c>
       <c r="V13" t="n">
         <v>-3.2017</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.838200000000001</v>
+        <v>10.5288</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8635</v>
+        <v>7.6822</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9747</v>
+        <v>2.8466</v>
       </c>
       <c r="G14" t="n">
         <v>6.3015</v>
@@ -1546,13 +1546,13 @@
         <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1438</v>
+        <v>0.8344</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8381</v>
+        <v>-0.0194</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9819</v>
+        <v>0.8538</v>
       </c>
       <c r="V14" t="n">
         <v>1.4344</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6755</v>
+        <v>8.0878</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0526</v>
+        <v>6.8713</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6229</v>
+        <v>1.2166</v>
       </c>
       <c r="G15" t="n">
         <v>7.2222</v>
@@ -1624,13 +1624,13 @@
         <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8601</v>
+        <v>0.5523</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7017</v>
+        <v>0.117</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1584</v>
+        <v>0.4352</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6659</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2437</v>
+        <v>4.913</v>
       </c>
       <c r="E16" t="n">
-        <v>5.8054</v>
+        <v>5.9078</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5617</v>
+        <v>-0.9948</v>
       </c>
       <c r="G16" t="n">
         <v>1.6386</v>
@@ -1702,13 +1702,13 @@
         <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2198</v>
+        <v>0.4495</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0965</v>
+        <v>0.0059</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1233</v>
+        <v>0.4436</v>
       </c>
       <c r="V16" t="n">
         <v>2.4332</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4213</v>
+        <v>4.2058</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0799</v>
+        <v>2.5916</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3414</v>
+        <v>1.6143</v>
       </c>
       <c r="G17" t="n">
         <v>3.2783</v>
@@ -1780,13 +1780,13 @@
         <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4446</v>
+        <v>0.3399</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6599</v>
+        <v>-0.1482</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2153</v>
+        <v>0.4882</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4771</v>
+        <v>1.1316</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4134</v>
+        <v>1.7204</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9363</v>
+        <v>-0.5888</v>
       </c>
       <c r="G18" t="n">
         <v>0.5987</v>
@@ -1858,13 +1858,13 @@
         <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1424</v>
+        <v>0.5121</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2488</v>
+        <v>0.5558</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3912</v>
+        <v>-0.0437</v>
       </c>
       <c r="V18" t="n">
         <v>0.6083</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SANJURJO BOTEJARA</t>
+          <t>L. GARCIA DE SANTIAGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1231</v>
+        <v>-0.1907</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4177</v>
+        <v>-0.1188</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5408</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0874</v>
+        <v>0.0052</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2539</v>
+        <v>0.2729</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8335</v>
+        <v>-0.2677</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1071</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6674</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4397</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0197</v>
+        <v>0.0052</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4135</v>
+        <v>0.2729</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3938</v>
+        <v>-0.2677</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3709</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5875</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.306</v>
+        <v>-0.1958</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3725</v>
+        <v>-0.1188</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9335</v>
+        <v>-0.077</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. GARCIA DE SANTIAGO</t>
+          <t>A. LOIRA PINHEIRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1907</v>
+        <v>-1.0093</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1188</v>
+        <v>-0.7416</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.2677</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0052</v>
+        <v>-0.8135</v>
       </c>
       <c r="H20" t="n">
         <v>0.2729</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2677</v>
+        <v>-1.0864</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.6822</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.6822</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0052</v>
+        <v>-0.1313</v>
       </c>
       <c r="N20" t="n">
         <v>0.2729</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2677</v>
+        <v>-0.4042</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2017,10 +2017,10 @@
         <v>-0.1958</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1188</v>
+        <v>-0.0594</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.077</v>
+        <v>-0.1364</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LOIRA PINHEIRO</t>
+          <t>P. SANJURJO BOTEJARA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0093</v>
+        <v>-1.4303</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7416</v>
+        <v>-2.5434</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2677</v>
+        <v>1.1131</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8135</v>
+        <v>-2.0874</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2729</v>
+        <v>-1.2539</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0864</v>
+        <v>-0.8335</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6822</v>
+        <v>-2.1071</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-1.6674</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6822</v>
+        <v>-0.4397</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1313</v>
+        <v>0.0197</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2729</v>
+        <v>0.4135</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4042</v>
+        <v>-0.3938</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1958</v>
+        <v>1.7526</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0594</v>
+        <v>1.2468</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1364</v>
+        <v>0.5058</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>X. QUINTELA VALCARCEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1659</v>
+        <v>-2.5833</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8233</v>
+        <v>-3.3928</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3426</v>
+        <v>0.8095</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6109</v>
+        <v>-1.3512</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.8289</v>
+        <v>-1.5332</v>
       </c>
       <c r="I22" t="n">
-        <v>1.218</v>
+        <v>0.1821</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2161</v>
+        <v>-1.9042</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.6759</v>
+        <v>-1.9446</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4598</v>
+        <v>0.0404</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3948</v>
+        <v>0.5531</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.153</v>
+        <v>0.4114</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2417</v>
+        <v>0.1416</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5668</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6201</v>
+        <v>0.4142</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1139</v>
+        <v>0.4699</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5062</v>
+        <v>-0.0557</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6083</v>
+        <v>-0.2754</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8249</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X. QUINTELA VALCARCEL</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3565</v>
+        <v>-3.2326</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0858</v>
+        <v>-1.949</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7292999999999999</v>
+        <v>-1.2835</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3512</v>
+        <v>-1.6109</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5332</v>
+        <v>-2.8289</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1821</v>
+        <v>1.218</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9042</v>
+        <v>-0.2161</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9446</v>
+        <v>-1.6759</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0404</v>
+        <v>1.4598</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5531</v>
+        <v>-1.3948</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4114</v>
+        <v>-1.153</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1416</v>
+        <v>-0.2417</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3709</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>0.641</v>
+        <v>0.5534</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7769</v>
+        <v>-0.0118</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1359</v>
+        <v>0.5652</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2754</v>
+        <v>-0.6083</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2754</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>19.0565</v>
+        <v>20.4208</v>
       </c>
       <c r="E24" t="n">
-        <v>16.0276</v>
+        <v>16.0277</v>
       </c>
       <c r="F24" t="n">
-        <v>3.0289</v>
+        <v>4.393400000000001</v>
       </c>
       <c r="G24" t="n">
         <v>13.1815</v>
@@ -2326,13 +2326,13 @@
         <v>9.792300000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6524</v>
+        <v>5.0168</v>
       </c>
       <c r="T24" t="n">
-        <v>2.0377</v>
+        <v>2.0378</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6147</v>
+        <v>2.979</v>
       </c>
       <c r="V24" t="n">
         <v>3.2017</v>
